--- a/branches/migration/2026.0.1-template-v0.11.3/observations-summary.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="65">
   <si>
     <t>Profile</t>
   </si>
@@ -104,6 +104,33 @@
     <t>SNOMED CT#842009</t>
   </si>
   <si>
+    <t>mii-pr-seltene-geburtsgewicht</t>
+  </si>
+  <si>
+    <t>MII PR SE Geburtsgewicht</t>
+  </si>
+  <si>
+    <t>LOINC#8339-4</t>
+  </si>
+  <si>
+    <t>mii-pr-seltene-geburtslaenge</t>
+  </si>
+  <si>
+    <t>MII PR SE Geburtslänge</t>
+  </si>
+  <si>
+    <t>LOINC#89269-5</t>
+  </si>
+  <si>
+    <t>mii-pr-seltene-gestationsalter</t>
+  </si>
+  <si>
+    <t>MII PR SE Gestationsalter bei Geburt</t>
+  </si>
+  <si>
+    <t>LOINC#76516-4</t>
+  </si>
+  <si>
     <t>mii-pr-seltene-hueftumfang</t>
   </si>
   <si>
@@ -111,6 +138,45 @@
   </si>
   <si>
     <t>LOINC#56063-1</t>
+  </si>
+  <si>
+    <t>mii-pr-seltene-icf-assessment</t>
+  </si>
+  <si>
+    <t>MII PR SE ICF Assessment</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#survey</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-icf (required)</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#extent-of-impairment</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#extent-of-impairment-structure</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#nature-of-change</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#anatomical-location</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#capacity</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#performance</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#barrier</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#facilitator</t>
   </si>
   <si>
     <t>mii-pr-seltene-kopfumfang</t>
@@ -274,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -460,28 +526,28 @@
         <v>34</v>
       </c>
       <c r="C6" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="F6" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s" s="2">
         <v>14</v>
@@ -489,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>14</v>
@@ -519,6 +585,426 @@
         <v>14</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/branches/migration/2026.0.1-template-v0.11.3/observations-summary.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/observations-summary.xlsx
@@ -137,7 +137,7 @@
     <t>MII PR SE Hüftumfang</t>
   </si>
   <si>
-    <t>LOINC#56063-1</t>
+    <t>SNOMED CT#284472007</t>
   </si>
   <si>
     <t>mii-pr-seltene-icf-assessment</t>
@@ -206,7 +206,7 @@
     <t>MII PR SE Taillenumfang</t>
   </si>
   <si>
-    <t>LOINC#8280-0</t>
+    <t>SNOMED CT#276361009</t>
   </si>
 </sst>
 </file>
